--- a/improvement/manufacturing/plan-10.xlsx
+++ b/improvement/manufacturing/plan-10.xlsx
@@ -538,7 +538,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>28名（うち製造現場20名・検査3名）</t>
+          <t>18名（うち製造現場12名・検査2名）</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>50万円（通常枠。賃金引上げ枠は200万円）</t>
+          <t>50万円（通常枠）。賃金引上げ特例等の上乗せ額は公募回ごとに異なる</t>
         </is>
       </c>
     </row>
